--- a/Scripts_inesdattatreya/data_output/session_2025-10with_classes.xlsx
+++ b/Scripts_inesdattatreya/data_output/session_2025-10with_classes.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>lca_class</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="Z4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="Z5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="Z7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="Z8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="Z11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Z15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="Z17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="Z18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="Z19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="Z20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="Z22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3266,6 +3266,9 @@
         <is>
           <t>2025-10</t>
         </is>
+      </c>
+      <c r="Z24">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
